--- a/basedatos_partidas/salida/descompuestos/07.04.01.030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.04.01.030.xlsx
@@ -584,7 +584,7 @@
         <v>0.016</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>0.08</v>
@@ -610,10 +610,10 @@
         <v>0.03</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="13">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="15">
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="H25" t="n">
         <v>0.03</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
     </row>
   </sheetData>
